--- a/procurement/bill-of-materials.xlsx
+++ b/procurement/bill-of-materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zbrozek-git\solarcar-batterypack\procurement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873C4282-B5BC-4CF7-A95E-5DC91763323E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A531B4-DD6B-46DE-A799-054B52873B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4120" yWindow="4480" windowWidth="23060" windowHeight="15160" xr2:uid="{D1D39CC7-F0DC-4302-817C-72372F10019E}"/>
+    <workbookView xWindow="4350" yWindow="1240" windowWidth="28200" windowHeight="18290" xr2:uid="{D1D39CC7-F0DC-4302-817C-72372F10019E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="137">
   <si>
     <t>Item</t>
   </si>
@@ -328,6 +328,123 @@
   </si>
   <si>
     <t>End terminal collector plate of cell stack</t>
+  </si>
+  <si>
+    <t>M3x25 Torx</t>
+  </si>
+  <si>
+    <t>Vicor retention</t>
+  </si>
+  <si>
+    <t>90362A156</t>
+  </si>
+  <si>
+    <t>One bottle is enough for a little bit more than one module.</t>
+  </si>
+  <si>
+    <t>M3x6 Torx</t>
+  </si>
+  <si>
+    <t>Fan adapter PCB retention</t>
+  </si>
+  <si>
+    <t>90362A113</t>
+  </si>
+  <si>
+    <t>94459A769</t>
+  </si>
+  <si>
+    <t>M3x3.4 brass heat-set insert</t>
+  </si>
+  <si>
+    <t>M4 10-14 AWG ring terminal</t>
+  </si>
+  <si>
+    <t>BMS mainboard to wire connection</t>
+  </si>
+  <si>
+    <t>277-11157-ND</t>
+  </si>
+  <si>
+    <t>B07Z4S98J4</t>
+  </si>
+  <si>
+    <t>Red &amp; black 10 AWG silicone wire</t>
+  </si>
+  <si>
+    <t>Highly flexible to make internal box routing easier.</t>
+  </si>
+  <si>
+    <t>Phoenix Contact 3240083.</t>
+  </si>
+  <si>
+    <t>M4x8 Torx</t>
+  </si>
+  <si>
+    <t>BMS mainboard wire fasteners</t>
+  </si>
+  <si>
+    <t>M4 washer</t>
+  </si>
+  <si>
+    <t>90362A118</t>
+  </si>
+  <si>
+    <t>93475A230</t>
+  </si>
+  <si>
+    <t>This is almost certainly severe overkill.</t>
+  </si>
+  <si>
+    <t>BMS mainboard PCB retention</t>
+  </si>
+  <si>
+    <t>BMS mainboard to enclosure wire connection</t>
+  </si>
+  <si>
+    <t>M4 6 AWG ring terminal</t>
+  </si>
+  <si>
+    <t>BMS mainboard to bus bar wire connection</t>
+  </si>
+  <si>
+    <t>Molex 0191930200.</t>
+  </si>
+  <si>
+    <t>WM7288-ND</t>
+  </si>
+  <si>
+    <t>M6 6 AWG ring terminal</t>
+  </si>
+  <si>
+    <t>Bus bar to bus bar wire connection</t>
+  </si>
+  <si>
+    <t>277-11163-ND</t>
+  </si>
+  <si>
+    <t>Phoenix Contact 3240090.</t>
+  </si>
+  <si>
+    <t>BMS Ampseal to plate fastener</t>
+  </si>
+  <si>
+    <t>99397A351</t>
+  </si>
+  <si>
+    <t>M2.63x8 thread-forming Torx</t>
+  </si>
+  <si>
+    <t>B09ZTFHNLD</t>
+  </si>
+  <si>
+    <t>BMS mainboard to bus bar wires</t>
+  </si>
+  <si>
+    <t>BMS mainboard to HVA280 wires</t>
+  </si>
+  <si>
+    <t>Red &amp; black 6 AWG silicone wire</t>
   </si>
 </sst>
 </file>
@@ -385,7 +502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
@@ -399,7 +516,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -716,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E35AEF16-A3B2-4455-A345-C04362318443}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.08984375" customWidth="1"/>
@@ -724,7 +840,7 @@
     <col min="3" max="3" width="44.81640625" customWidth="1"/>
     <col min="4" max="4" width="15.6328125" customWidth="1"/>
     <col min="5" max="5" width="22.6328125" customWidth="1"/>
-    <col min="6" max="6" width="41.7265625" customWidth="1"/>
+    <col min="6" max="6" width="55.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -748,62 +864,62 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>30</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>95</v>
       </c>
     </row>
@@ -983,6 +1099,9 @@
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="F13" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -1020,7 +1139,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
         <v>46</v>
@@ -1035,7 +1154,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1237,72 +1356,332 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>71</v>
+        <v>4</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
+      </c>
+      <c r="F28" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
+      </c>
+      <c r="F29" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>8</v>
+      </c>
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" t="s">
+        <v>135</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F36" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>8</v>
+      </c>
+      <c r="B39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>32</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F43" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1328,15 +1707,28 @@
     <hyperlink ref="E25" r:id="rId18" xr:uid="{AB1ACC5D-5ECA-4059-97DC-2E8EF8A5445D}"/>
     <hyperlink ref="E15" r:id="rId19" xr:uid="{3222BA2C-3B4D-422B-8D97-181484BB8594}"/>
     <hyperlink ref="E26" r:id="rId20" xr:uid="{053324CF-C718-4D69-AEFA-5147FC0FBCF2}"/>
-    <hyperlink ref="E27" r:id="rId21" xr:uid="{703C9D90-A3FF-4161-9E71-74EA7EEEA3AF}"/>
-    <hyperlink ref="E28" r:id="rId22" xr:uid="{79B816E4-8BA2-4BB2-B192-BE5E7BF8F531}"/>
+    <hyperlink ref="E40" r:id="rId21" xr:uid="{703C9D90-A3FF-4161-9E71-74EA7EEEA3AF}"/>
+    <hyperlink ref="E41" r:id="rId22" xr:uid="{79B816E4-8BA2-4BB2-B192-BE5E7BF8F531}"/>
     <hyperlink ref="E7" r:id="rId23" display="https://www.homedepot.com/p/Frost-King-5-16-in-x-1-4-in-x-17-ft-Black-EPDM-Cellular-Rubber-Weatherstrip-Tape-V25BK/202844545" xr:uid="{FEA02C46-683D-40C3-8669-86F64F07737F}"/>
-    <hyperlink ref="E29" r:id="rId24" xr:uid="{0B4DDB7F-BCD6-433C-8493-C69541381BDE}"/>
+    <hyperlink ref="E42" r:id="rId24" xr:uid="{0B4DDB7F-BCD6-433C-8493-C69541381BDE}"/>
     <hyperlink ref="E17" r:id="rId25" xr:uid="{5D8DA4CF-D7DA-447D-A6E9-6C590F96EB07}"/>
-    <hyperlink ref="E30" r:id="rId26" xr:uid="{047ED4CC-5C21-4626-88F6-5FC8BF717D42}"/>
+    <hyperlink ref="E43" r:id="rId26" xr:uid="{047ED4CC-5C21-4626-88F6-5FC8BF717D42}"/>
     <hyperlink ref="D2" r:id="rId27" xr:uid="{5EA29408-AF76-4487-95D5-EBA6B359D47F}"/>
     <hyperlink ref="D3" r:id="rId28" xr:uid="{96CB2BCC-A5EC-485B-9D31-0A951023FBEE}"/>
     <hyperlink ref="D4" r:id="rId29" xr:uid="{8EEA5B90-7272-496A-8B8E-05147344EE67}"/>
+    <hyperlink ref="E27" r:id="rId30" xr:uid="{EDF89984-41DC-428C-8A06-A5219D2F2064}"/>
+    <hyperlink ref="E28" r:id="rId31" xr:uid="{963EF514-45F6-41B5-8A0B-170A2C5ED925}"/>
+    <hyperlink ref="E29" r:id="rId32" xr:uid="{0541AB64-B50E-4219-BAEB-29954AE6C189}"/>
+    <hyperlink ref="E32" r:id="rId33" xr:uid="{601039D8-147B-4A85-B635-6E59BA7A2244}"/>
+    <hyperlink ref="E36" r:id="rId34" xr:uid="{7564D6D7-CED9-4D38-BBD7-C2EEA78F1308}"/>
+    <hyperlink ref="E34" r:id="rId35" xr:uid="{F1B28719-9C73-4CA8-91D4-84394F1BF02D}"/>
+    <hyperlink ref="E33" r:id="rId36" xr:uid="{46B0625B-ED5E-40A2-8233-AF6C3C10EBD9}"/>
+    <hyperlink ref="E37" r:id="rId37" xr:uid="{6624FAE6-B969-40BE-A83C-00E8C8E8107F}"/>
+    <hyperlink ref="E38" r:id="rId38" xr:uid="{FCDD24C9-7BEC-4ED4-879C-62F1D5248DE6}"/>
+    <hyperlink ref="E31" r:id="rId39" xr:uid="{E368D647-630A-427B-B878-286A42748400}"/>
+    <hyperlink ref="E30" r:id="rId40" xr:uid="{E2835FD3-57C4-45F7-AADC-A649C55446B5}"/>
+    <hyperlink ref="E39" r:id="rId41" xr:uid="{08C6F825-C2F3-4C5A-9844-FCA3A713F68D}"/>
+    <hyperlink ref="E35" r:id="rId42" xr:uid="{D152971E-7BC5-4FDF-AC3C-70B542BD6FCF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/procurement/bill-of-materials.xlsx
+++ b/procurement/bill-of-materials.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zbrozek-git\solarcar-batterypack\procurement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A531B4-DD6B-46DE-A799-054B52873B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183C7ED8-29EC-40BF-85FF-1A1511BFCB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4350" yWindow="1240" windowWidth="28200" windowHeight="18290" xr2:uid="{D1D39CC7-F0DC-4302-817C-72372F10019E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D1D39CC7-F0DC-4302-817C-72372F10019E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="138">
   <si>
     <t>Item</t>
   </si>
@@ -445,6 +445,9 @@
   </si>
   <si>
     <t>Red &amp; black 6 AWG silicone wire</t>
+  </si>
+  <si>
+    <t>BMS security tape frame retention</t>
   </si>
 </sst>
 </file>
@@ -832,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E35AEF16-A3B2-4455-A345-C04362318443}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.08984375" customWidth="1"/>
@@ -1616,19 +1619,22 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>71</v>
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -1636,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C41" t="s">
         <v>70</v>
@@ -1644,44 +1650,61 @@
       <c r="D41" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>73</v>
+      <c r="E41" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D42" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D43" t="s">
         <v>16</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>1</v>
+      </c>
+      <c r="B44" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F44" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1707,12 +1730,12 @@
     <hyperlink ref="E25" r:id="rId18" xr:uid="{AB1ACC5D-5ECA-4059-97DC-2E8EF8A5445D}"/>
     <hyperlink ref="E15" r:id="rId19" xr:uid="{3222BA2C-3B4D-422B-8D97-181484BB8594}"/>
     <hyperlink ref="E26" r:id="rId20" xr:uid="{053324CF-C718-4D69-AEFA-5147FC0FBCF2}"/>
-    <hyperlink ref="E40" r:id="rId21" xr:uid="{703C9D90-A3FF-4161-9E71-74EA7EEEA3AF}"/>
-    <hyperlink ref="E41" r:id="rId22" xr:uid="{79B816E4-8BA2-4BB2-B192-BE5E7BF8F531}"/>
+    <hyperlink ref="E41" r:id="rId21" xr:uid="{703C9D90-A3FF-4161-9E71-74EA7EEEA3AF}"/>
+    <hyperlink ref="E42" r:id="rId22" xr:uid="{79B816E4-8BA2-4BB2-B192-BE5E7BF8F531}"/>
     <hyperlink ref="E7" r:id="rId23" display="https://www.homedepot.com/p/Frost-King-5-16-in-x-1-4-in-x-17-ft-Black-EPDM-Cellular-Rubber-Weatherstrip-Tape-V25BK/202844545" xr:uid="{FEA02C46-683D-40C3-8669-86F64F07737F}"/>
-    <hyperlink ref="E42" r:id="rId24" xr:uid="{0B4DDB7F-BCD6-433C-8493-C69541381BDE}"/>
+    <hyperlink ref="E43" r:id="rId24" xr:uid="{0B4DDB7F-BCD6-433C-8493-C69541381BDE}"/>
     <hyperlink ref="E17" r:id="rId25" xr:uid="{5D8DA4CF-D7DA-447D-A6E9-6C590F96EB07}"/>
-    <hyperlink ref="E43" r:id="rId26" xr:uid="{047ED4CC-5C21-4626-88F6-5FC8BF717D42}"/>
+    <hyperlink ref="E44" r:id="rId26" xr:uid="{047ED4CC-5C21-4626-88F6-5FC8BF717D42}"/>
     <hyperlink ref="D2" r:id="rId27" xr:uid="{5EA29408-AF76-4487-95D5-EBA6B359D47F}"/>
     <hyperlink ref="D3" r:id="rId28" xr:uid="{96CB2BCC-A5EC-485B-9D31-0A951023FBEE}"/>
     <hyperlink ref="D4" r:id="rId29" xr:uid="{8EEA5B90-7272-496A-8B8E-05147344EE67}"/>
@@ -1729,6 +1752,7 @@
     <hyperlink ref="E30" r:id="rId40" xr:uid="{E2835FD3-57C4-45F7-AADC-A649C55446B5}"/>
     <hyperlink ref="E39" r:id="rId41" xr:uid="{08C6F825-C2F3-4C5A-9844-FCA3A713F68D}"/>
     <hyperlink ref="E35" r:id="rId42" xr:uid="{D152971E-7BC5-4FDF-AC3C-70B542BD6FCF}"/>
+    <hyperlink ref="E40" r:id="rId43" xr:uid="{EE360B1E-4D3C-4B17-BE11-666C855307BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/procurement/bill-of-materials.xlsx
+++ b/procurement/bill-of-materials.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zbrozek-git\solarcar-batterypack\procurement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thisuser\Documents\zbrozek-git\solarcar-batterypack\procurement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183C7ED8-29EC-40BF-85FF-1A1511BFCB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FD03A8-428A-4275-980D-EF3ED49CA0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D1D39CC7-F0DC-4302-817C-72372F10019E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{D1D39CC7-F0DC-4302-817C-72372F10019E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
+    <sheet name="Race service hardware" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="145">
   <si>
     <t>Item</t>
   </si>
@@ -279,9 +280,6 @@
     <t>BC2792-ND</t>
   </si>
   <si>
-    <t>47k NTC thermistor</t>
-  </si>
-  <si>
     <t>High viscosity cyanoacrylate glue</t>
   </si>
   <si>
@@ -448,13 +446,37 @@
   </si>
   <si>
     <t>BMS security tape frame retention</t>
+  </si>
+  <si>
+    <t>10k NTC thermistor</t>
+  </si>
+  <si>
+    <t>M4x18 socket head</t>
+  </si>
+  <si>
+    <t>HVA280 retention</t>
+  </si>
+  <si>
+    <t>91292A043</t>
+  </si>
+  <si>
+    <t>M4 flat washer</t>
+  </si>
+  <si>
+    <t>Noctua 60mm 4-wire fan</t>
+  </si>
+  <si>
+    <t>B00VXTANZ4</t>
+  </si>
+  <si>
+    <t>This is more reasonable.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,6 +505,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -505,7 +544,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
@@ -520,6 +559,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -835,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E35AEF16-A3B2-4455-A345-C04362318443}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.08984375" customWidth="1"/>
@@ -871,19 +912,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -891,19 +932,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -911,19 +952,19 @@
         <v>30</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="F4" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1087,40 +1128,43 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13">
+      <c r="A13" s="8">
         <v>2</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F13" t="s">
-        <v>119</v>
+      <c r="F13" s="8" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>53</v>
+        <v>143</v>
+      </c>
+      <c r="F14" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1128,73 +1172,73 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>54</v>
+        <v>83</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1202,7 +1246,7 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
         <v>56</v>
@@ -1211,50 +1255,47 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1262,39 +1303,39 @@
         <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1302,56 +1343,56 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s">
         <v>61</v>
@@ -1359,19 +1400,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="F27" t="s">
         <v>39</v>
@@ -1379,19 +1420,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
         <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F28" t="s">
         <v>39</v>
@@ -1399,19 +1440,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="F29" t="s">
         <v>61</v>
@@ -1419,119 +1460,119 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s">
-        <v>129</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="F31" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F32" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="F35" t="s">
         <v>112</v>
@@ -1539,39 +1580,39 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="D36" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C37" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D37" t="s">
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F37" t="s">
         <v>39</v>
@@ -1579,113 +1620,122 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D38" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F38" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="F39" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D40" t="s">
         <v>4</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>71</v>
+        <v>4</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>73</v>
+        <v>130</v>
+      </c>
+      <c r="F42" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>80</v>
+        <v>59</v>
+      </c>
+      <c r="F43" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -1693,19 +1743,70 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D44" t="s">
         <v>16</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>1</v>
+      </c>
+      <c r="B45" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" t="s">
+        <v>85</v>
+      </c>
+      <c r="D47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" t="s">
         <v>87</v>
-      </c>
-      <c r="F44" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1716,43 +1817,142 @@
     <hyperlink ref="E11" r:id="rId4" xr:uid="{1341B924-4CE8-49B4-9879-70C36D703B9B}"/>
     <hyperlink ref="E12" r:id="rId5" xr:uid="{DB715325-A5E8-4142-91C1-CB4D7671EAC4}"/>
     <hyperlink ref="E13" r:id="rId6" xr:uid="{C9F8F54D-633F-4EC9-906D-512C3ECB3C9D}"/>
-    <hyperlink ref="E20" r:id="rId7" xr:uid="{5F669C13-254A-4366-88C8-AA954A1FD248}"/>
+    <hyperlink ref="E21" r:id="rId7" xr:uid="{5F669C13-254A-4366-88C8-AA954A1FD248}"/>
     <hyperlink ref="E6" r:id="rId8" xr:uid="{1720EDB6-2970-4234-AE8D-A2EB8A1E4656}"/>
     <hyperlink ref="E5" r:id="rId9" xr:uid="{7D9406DF-30E4-4CB4-BC64-6E5EF5394722}"/>
-    <hyperlink ref="E21" r:id="rId10" xr:uid="{A8CBEDD8-2E52-43E4-A6E4-AAC989359F3C}"/>
-    <hyperlink ref="E23" r:id="rId11" xr:uid="{00ED004B-BEF3-46D4-A9F1-5653CB0ECACE}"/>
-    <hyperlink ref="E24" r:id="rId12" xr:uid="{90BD5053-64C3-411A-824F-C52830C9ECEE}"/>
-    <hyperlink ref="E22" r:id="rId13" xr:uid="{08478DE1-4B7B-44A2-84F2-792CDB4E2BB7}"/>
-    <hyperlink ref="E16" r:id="rId14" xr:uid="{97BDC9BA-AA2A-4B79-9AF3-1FDB238A5DD8}"/>
-    <hyperlink ref="E14" r:id="rId15" xr:uid="{4D4ED1A0-014D-46E6-A815-F83D9669D738}"/>
-    <hyperlink ref="E18" r:id="rId16" xr:uid="{2A22CCB5-BC72-4BAA-BCEC-A4DC45084DBF}"/>
-    <hyperlink ref="E19" r:id="rId17" xr:uid="{762ABCE6-56DE-493E-8A2B-C9627A1FE13E}"/>
-    <hyperlink ref="E25" r:id="rId18" xr:uid="{AB1ACC5D-5ECA-4059-97DC-2E8EF8A5445D}"/>
-    <hyperlink ref="E15" r:id="rId19" xr:uid="{3222BA2C-3B4D-422B-8D97-181484BB8594}"/>
-    <hyperlink ref="E26" r:id="rId20" xr:uid="{053324CF-C718-4D69-AEFA-5147FC0FBCF2}"/>
-    <hyperlink ref="E41" r:id="rId21" xr:uid="{703C9D90-A3FF-4161-9E71-74EA7EEEA3AF}"/>
-    <hyperlink ref="E42" r:id="rId22" xr:uid="{79B816E4-8BA2-4BB2-B192-BE5E7BF8F531}"/>
+    <hyperlink ref="E22" r:id="rId10" xr:uid="{A8CBEDD8-2E52-43E4-A6E4-AAC989359F3C}"/>
+    <hyperlink ref="E24" r:id="rId11" xr:uid="{00ED004B-BEF3-46D4-A9F1-5653CB0ECACE}"/>
+    <hyperlink ref="E25" r:id="rId12" xr:uid="{90BD5053-64C3-411A-824F-C52830C9ECEE}"/>
+    <hyperlink ref="E23" r:id="rId13" xr:uid="{08478DE1-4B7B-44A2-84F2-792CDB4E2BB7}"/>
+    <hyperlink ref="E17" r:id="rId14" xr:uid="{97BDC9BA-AA2A-4B79-9AF3-1FDB238A5DD8}"/>
+    <hyperlink ref="E15" r:id="rId15" xr:uid="{4D4ED1A0-014D-46E6-A815-F83D9669D738}"/>
+    <hyperlink ref="E19" r:id="rId16" xr:uid="{2A22CCB5-BC72-4BAA-BCEC-A4DC45084DBF}"/>
+    <hyperlink ref="E20" r:id="rId17" xr:uid="{762ABCE6-56DE-493E-8A2B-C9627A1FE13E}"/>
+    <hyperlink ref="E26" r:id="rId18" xr:uid="{AB1ACC5D-5ECA-4059-97DC-2E8EF8A5445D}"/>
+    <hyperlink ref="E16" r:id="rId19" xr:uid="{3222BA2C-3B4D-422B-8D97-181484BB8594}"/>
+    <hyperlink ref="E29" r:id="rId20" xr:uid="{053324CF-C718-4D69-AEFA-5147FC0FBCF2}"/>
+    <hyperlink ref="E44" r:id="rId21" xr:uid="{703C9D90-A3FF-4161-9E71-74EA7EEEA3AF}"/>
+    <hyperlink ref="E45" r:id="rId22" xr:uid="{79B816E4-8BA2-4BB2-B192-BE5E7BF8F531}"/>
     <hyperlink ref="E7" r:id="rId23" display="https://www.homedepot.com/p/Frost-King-5-16-in-x-1-4-in-x-17-ft-Black-EPDM-Cellular-Rubber-Weatherstrip-Tape-V25BK/202844545" xr:uid="{FEA02C46-683D-40C3-8669-86F64F07737F}"/>
-    <hyperlink ref="E43" r:id="rId24" xr:uid="{0B4DDB7F-BCD6-433C-8493-C69541381BDE}"/>
-    <hyperlink ref="E17" r:id="rId25" xr:uid="{5D8DA4CF-D7DA-447D-A6E9-6C590F96EB07}"/>
-    <hyperlink ref="E44" r:id="rId26" xr:uid="{047ED4CC-5C21-4626-88F6-5FC8BF717D42}"/>
+    <hyperlink ref="E46" r:id="rId24" xr:uid="{0B4DDB7F-BCD6-433C-8493-C69541381BDE}"/>
+    <hyperlink ref="E18" r:id="rId25" xr:uid="{5D8DA4CF-D7DA-447D-A6E9-6C590F96EB07}"/>
+    <hyperlink ref="E47" r:id="rId26" xr:uid="{047ED4CC-5C21-4626-88F6-5FC8BF717D42}"/>
     <hyperlink ref="D2" r:id="rId27" xr:uid="{5EA29408-AF76-4487-95D5-EBA6B359D47F}"/>
     <hyperlink ref="D3" r:id="rId28" xr:uid="{96CB2BCC-A5EC-485B-9D31-0A951023FBEE}"/>
     <hyperlink ref="D4" r:id="rId29" xr:uid="{8EEA5B90-7272-496A-8B8E-05147344EE67}"/>
-    <hyperlink ref="E27" r:id="rId30" xr:uid="{EDF89984-41DC-428C-8A06-A5219D2F2064}"/>
-    <hyperlink ref="E28" r:id="rId31" xr:uid="{963EF514-45F6-41B5-8A0B-170A2C5ED925}"/>
-    <hyperlink ref="E29" r:id="rId32" xr:uid="{0541AB64-B50E-4219-BAEB-29954AE6C189}"/>
-    <hyperlink ref="E32" r:id="rId33" xr:uid="{601039D8-147B-4A85-B635-6E59BA7A2244}"/>
-    <hyperlink ref="E36" r:id="rId34" xr:uid="{7564D6D7-CED9-4D38-BBD7-C2EEA78F1308}"/>
-    <hyperlink ref="E34" r:id="rId35" xr:uid="{F1B28719-9C73-4CA8-91D4-84394F1BF02D}"/>
-    <hyperlink ref="E33" r:id="rId36" xr:uid="{46B0625B-ED5E-40A2-8233-AF6C3C10EBD9}"/>
-    <hyperlink ref="E37" r:id="rId37" xr:uid="{6624FAE6-B969-40BE-A83C-00E8C8E8107F}"/>
-    <hyperlink ref="E38" r:id="rId38" xr:uid="{FCDD24C9-7BEC-4ED4-879C-62F1D5248DE6}"/>
-    <hyperlink ref="E31" r:id="rId39" xr:uid="{E368D647-630A-427B-B878-286A42748400}"/>
-    <hyperlink ref="E30" r:id="rId40" xr:uid="{E2835FD3-57C4-45F7-AADC-A649C55446B5}"/>
-    <hyperlink ref="E39" r:id="rId41" xr:uid="{08C6F825-C2F3-4C5A-9844-FCA3A713F68D}"/>
-    <hyperlink ref="E35" r:id="rId42" xr:uid="{D152971E-7BC5-4FDF-AC3C-70B542BD6FCF}"/>
-    <hyperlink ref="E40" r:id="rId43" xr:uid="{EE360B1E-4D3C-4B17-BE11-666C855307BC}"/>
+    <hyperlink ref="E30" r:id="rId30" xr:uid="{EDF89984-41DC-428C-8A06-A5219D2F2064}"/>
+    <hyperlink ref="E31" r:id="rId31" xr:uid="{963EF514-45F6-41B5-8A0B-170A2C5ED925}"/>
+    <hyperlink ref="E32" r:id="rId32" xr:uid="{0541AB64-B50E-4219-BAEB-29954AE6C189}"/>
+    <hyperlink ref="E35" r:id="rId33" xr:uid="{601039D8-147B-4A85-B635-6E59BA7A2244}"/>
+    <hyperlink ref="E39" r:id="rId34" xr:uid="{7564D6D7-CED9-4D38-BBD7-C2EEA78F1308}"/>
+    <hyperlink ref="E37" r:id="rId35" xr:uid="{F1B28719-9C73-4CA8-91D4-84394F1BF02D}"/>
+    <hyperlink ref="E36" r:id="rId36" xr:uid="{46B0625B-ED5E-40A2-8233-AF6C3C10EBD9}"/>
+    <hyperlink ref="E40" r:id="rId37" xr:uid="{6624FAE6-B969-40BE-A83C-00E8C8E8107F}"/>
+    <hyperlink ref="E41" r:id="rId38" xr:uid="{FCDD24C9-7BEC-4ED4-879C-62F1D5248DE6}"/>
+    <hyperlink ref="E34" r:id="rId39" xr:uid="{E368D647-630A-427B-B878-286A42748400}"/>
+    <hyperlink ref="E33" r:id="rId40" xr:uid="{E2835FD3-57C4-45F7-AADC-A649C55446B5}"/>
+    <hyperlink ref="E42" r:id="rId41" xr:uid="{08C6F825-C2F3-4C5A-9844-FCA3A713F68D}"/>
+    <hyperlink ref="E38" r:id="rId42" xr:uid="{D152971E-7BC5-4FDF-AC3C-70B542BD6FCF}"/>
+    <hyperlink ref="E43" r:id="rId43" xr:uid="{EE360B1E-4D3C-4B17-BE11-666C855307BC}"/>
+    <hyperlink ref="E27" r:id="rId44" xr:uid="{E88A01CD-9D0A-4CB0-B261-AD9782F0FDB5}"/>
+    <hyperlink ref="E28" r:id="rId45" xr:uid="{79E85FCD-9DE4-4D29-8E73-74087A5E1F26}"/>
+    <hyperlink ref="E14" r:id="rId46" xr:uid="{C6202BE2-BE15-4B76-8999-8AAA70770870}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="262" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId47"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35051E3-80A1-4EBE-808C-93CF2367A231}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{960FCF17-0FEC-4331-AFB1-F10FDFCF86FA}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{BDD3E217-9437-4B21-9A28-68965C92C2A9}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{FD5BC05D-18EA-4519-9D03-7C5500113CCF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/procurement/bill-of-materials.xlsx
+++ b/procurement/bill-of-materials.xlsx
@@ -1,41 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thisuser\Documents\zbrozek-git\solarcar-batterypack\procurement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\zbrozek-git\solarcar-batterypack\procurement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FD03A8-428A-4275-980D-EF3ED49CA0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C86C53-3017-462D-B3C8-E0F55DFBA87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{D1D39CC7-F0DC-4302-817C-72372F10019E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{D1D39CC7-F0DC-4302-817C-72372F10019E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
     <sheet name="Race service hardware" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="167">
   <si>
     <t>Item</t>
   </si>
@@ -73,9 +64,6 @@
     <t>B0CDGYTLH6</t>
   </si>
   <si>
-    <t>SS M5x14 thread-forming</t>
-  </si>
-  <si>
     <t>Fan mounting</t>
   </si>
   <si>
@@ -250,9 +238,6 @@
     <t>Box connector face</t>
   </si>
   <si>
-    <t>SAM9854-ND</t>
-  </si>
-  <si>
     <t>Ethernet dust cover</t>
   </si>
   <si>
@@ -382,9 +367,6 @@
     <t>BMS mainboard wire fasteners</t>
   </si>
   <si>
-    <t>M4 washer</t>
-  </si>
-  <si>
     <t>90362A118</t>
   </si>
   <si>
@@ -400,9 +382,6 @@
     <t>BMS mainboard to enclosure wire connection</t>
   </si>
   <si>
-    <t>M4 6 AWG ring terminal</t>
-  </si>
-  <si>
     <t>BMS mainboard to bus bar wire connection</t>
   </si>
   <si>
@@ -415,18 +394,12 @@
     <t>M6 6 AWG ring terminal</t>
   </si>
   <si>
-    <t>Bus bar to bus bar wire connection</t>
-  </si>
-  <si>
     <t>277-11163-ND</t>
   </si>
   <si>
     <t>Phoenix Contact 3240090.</t>
   </si>
   <si>
-    <t>BMS Ampseal to plate fastener</t>
-  </si>
-  <si>
     <t>99397A351</t>
   </si>
   <si>
@@ -470,6 +443,90 @@
   </si>
   <si>
     <t>This is more reasonable.</t>
+  </si>
+  <si>
+    <t>SAM9120-ND</t>
+  </si>
+  <si>
+    <t>M4 conical washer</t>
+  </si>
+  <si>
+    <t>91477A141</t>
+  </si>
+  <si>
+    <t>Red &amp; black 8 AWG silicone wire</t>
+  </si>
+  <si>
+    <t>BMS mainboard to HVA280 wires, if they fit.</t>
+  </si>
+  <si>
+    <t>B0BTLFNLLY</t>
+  </si>
+  <si>
+    <t>BMS Ampseal to front panel fastener</t>
+  </si>
+  <si>
+    <t>M5x14 thread-forming</t>
+  </si>
+  <si>
+    <t>Bus bar to wire connection</t>
+  </si>
+  <si>
+    <t>M4 6-8 AWG ring terminal</t>
+  </si>
+  <si>
+    <t>SCT-NO.2-E5-0-STK-ND</t>
+  </si>
+  <si>
+    <t>9 mm diameter adhesive heat shrink</t>
+  </si>
+  <si>
+    <t>Wire to ring terminal conections</t>
+  </si>
+  <si>
+    <t>94560A111</t>
+  </si>
+  <si>
+    <t>M3 flex-top lock nuts</t>
+  </si>
+  <si>
+    <t>BMS contactor coil connection</t>
+  </si>
+  <si>
+    <t>M4 flex-top lock nuts</t>
+  </si>
+  <si>
+    <t>BMS contactor current carrying connection</t>
+  </si>
+  <si>
+    <t>94560A112</t>
+  </si>
+  <si>
+    <t>M3 conical washer</t>
+  </si>
+  <si>
+    <t>Mcmaster</t>
+  </si>
+  <si>
+    <t>Sold each</t>
+  </si>
+  <si>
+    <t>M2 conical washer</t>
+  </si>
+  <si>
+    <t>Between AFE PCBA and screw head</t>
+  </si>
+  <si>
+    <t>91477A122</t>
+  </si>
+  <si>
+    <t>91477A121</t>
+  </si>
+  <si>
+    <t>BMS contactor coil connection, between nut and PCBA</t>
+  </si>
+  <si>
+    <t>BMS contactor current carrying connection, between nut and PCBA</t>
   </si>
 </sst>
 </file>
@@ -876,12 +933,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E35AEF16-A3B2-4455-A345-C04362318443}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.08984375" customWidth="1"/>
-    <col min="2" max="2" width="29.08984375" customWidth="1"/>
-    <col min="3" max="3" width="44.81640625" customWidth="1"/>
+    <col min="2" max="2" width="34.26953125" customWidth="1"/>
+    <col min="3" max="3" width="56.90625" customWidth="1"/>
     <col min="4" max="4" width="15.6328125" customWidth="1"/>
     <col min="5" max="5" width="22.6328125" customWidth="1"/>
     <col min="6" max="6" width="55.36328125" customWidth="1"/>
@@ -901,10 +958,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -912,19 +969,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -932,19 +989,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -952,19 +1009,19 @@
         <v>30</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -972,19 +1029,19 @@
         <v>8</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -992,19 +1049,19 @@
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1012,19 +1069,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E7" s="5">
         <v>625515</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1044,7 +1101,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1064,7 +1121,7 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1084,7 +1141,7 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1104,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1112,19 +1169,19 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1132,19 +1189,19 @@
         <v>2</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="F13" s="8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1152,19 +1209,19 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F14" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1172,16 +1229,16 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
         <v>50</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>51</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1189,16 +1246,16 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
         <v>63</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1206,19 +1263,19 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
         <v>46</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1226,19 +1283,19 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1246,16 +1303,16 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
         <v>55</v>
       </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
       <c r="D19" t="s">
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1263,19 +1320,19 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1283,19 +1340,19 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
         <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>21</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1303,19 +1360,19 @@
         <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1323,39 +1380,39 @@
         <v>64</v>
       </c>
       <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
         <v>43</v>
       </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
       <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>35</v>
+        <v>163</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -1363,59 +1420,59 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -1423,19 +1480,19 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
         <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -1443,59 +1500,59 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
         <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
         <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -1503,39 +1560,39 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -1546,13 +1603,13 @@
         <v>121</v>
       </c>
       <c r="C34" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="D34" t="s">
-        <v>16</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="F34" t="s">
         <v>123</v>
@@ -1560,142 +1617,142 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="F35" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="D36" t="s">
-        <v>4</v>
+        <v>159</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="D37" t="s">
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F38" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D40" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" t="s">
         <v>105</v>
       </c>
-      <c r="C41" t="s">
-        <v>119</v>
-      </c>
       <c r="D41" t="s">
         <v>4</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="F41" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -1703,39 +1760,39 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
         <v>4</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="F43" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -1743,16 +1800,19 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F44" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -1760,53 +1820,187 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>73</v>
+        <v>107</v>
+      </c>
+      <c r="F45" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>8</v>
+      </c>
+      <c r="B48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>2</v>
+      </c>
+      <c r="B49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50">
         <v>1</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B50" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>16</v>
+      </c>
+      <c r="B52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" t="s">
+        <v>72</v>
+      </c>
+      <c r="D52" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>1</v>
+      </c>
+      <c r="B53" t="s">
+        <v>82</v>
+      </c>
+      <c r="C53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C47" t="s">
+      <c r="F53" t="s">
         <v>85</v>
       </c>
-      <c r="D47" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F47" t="s">
-        <v>87</v>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1821,52 +2015,66 @@
     <hyperlink ref="E6" r:id="rId8" xr:uid="{1720EDB6-2970-4234-AE8D-A2EB8A1E4656}"/>
     <hyperlink ref="E5" r:id="rId9" xr:uid="{7D9406DF-30E4-4CB4-BC64-6E5EF5394722}"/>
     <hyperlink ref="E22" r:id="rId10" xr:uid="{A8CBEDD8-2E52-43E4-A6E4-AAC989359F3C}"/>
-    <hyperlink ref="E24" r:id="rId11" xr:uid="{00ED004B-BEF3-46D4-A9F1-5653CB0ECACE}"/>
-    <hyperlink ref="E25" r:id="rId12" xr:uid="{90BD5053-64C3-411A-824F-C52830C9ECEE}"/>
+    <hyperlink ref="E25" r:id="rId11" xr:uid="{00ED004B-BEF3-46D4-A9F1-5653CB0ECACE}"/>
+    <hyperlink ref="E26" r:id="rId12" xr:uid="{90BD5053-64C3-411A-824F-C52830C9ECEE}"/>
     <hyperlink ref="E23" r:id="rId13" xr:uid="{08478DE1-4B7B-44A2-84F2-792CDB4E2BB7}"/>
     <hyperlink ref="E17" r:id="rId14" xr:uid="{97BDC9BA-AA2A-4B79-9AF3-1FDB238A5DD8}"/>
     <hyperlink ref="E15" r:id="rId15" xr:uid="{4D4ED1A0-014D-46E6-A815-F83D9669D738}"/>
     <hyperlink ref="E19" r:id="rId16" xr:uid="{2A22CCB5-BC72-4BAA-BCEC-A4DC45084DBF}"/>
     <hyperlink ref="E20" r:id="rId17" xr:uid="{762ABCE6-56DE-493E-8A2B-C9627A1FE13E}"/>
-    <hyperlink ref="E26" r:id="rId18" xr:uid="{AB1ACC5D-5ECA-4059-97DC-2E8EF8A5445D}"/>
+    <hyperlink ref="E27" r:id="rId18" xr:uid="{AB1ACC5D-5ECA-4059-97DC-2E8EF8A5445D}"/>
     <hyperlink ref="E16" r:id="rId19" xr:uid="{3222BA2C-3B4D-422B-8D97-181484BB8594}"/>
-    <hyperlink ref="E29" r:id="rId20" xr:uid="{053324CF-C718-4D69-AEFA-5147FC0FBCF2}"/>
-    <hyperlink ref="E44" r:id="rId21" xr:uid="{703C9D90-A3FF-4161-9E71-74EA7EEEA3AF}"/>
-    <hyperlink ref="E45" r:id="rId22" xr:uid="{79B816E4-8BA2-4BB2-B192-BE5E7BF8F531}"/>
+    <hyperlink ref="E30" r:id="rId20" xr:uid="{053324CF-C718-4D69-AEFA-5147FC0FBCF2}"/>
+    <hyperlink ref="E50" r:id="rId21" xr:uid="{703C9D90-A3FF-4161-9E71-74EA7EEEA3AF}"/>
+    <hyperlink ref="E51" r:id="rId22" xr:uid="{79B816E4-8BA2-4BB2-B192-BE5E7BF8F531}"/>
     <hyperlink ref="E7" r:id="rId23" display="https://www.homedepot.com/p/Frost-King-5-16-in-x-1-4-in-x-17-ft-Black-EPDM-Cellular-Rubber-Weatherstrip-Tape-V25BK/202844545" xr:uid="{FEA02C46-683D-40C3-8669-86F64F07737F}"/>
-    <hyperlink ref="E46" r:id="rId24" xr:uid="{0B4DDB7F-BCD6-433C-8493-C69541381BDE}"/>
+    <hyperlink ref="E52" r:id="rId24" xr:uid="{0B4DDB7F-BCD6-433C-8493-C69541381BDE}"/>
     <hyperlink ref="E18" r:id="rId25" xr:uid="{5D8DA4CF-D7DA-447D-A6E9-6C590F96EB07}"/>
-    <hyperlink ref="E47" r:id="rId26" xr:uid="{047ED4CC-5C21-4626-88F6-5FC8BF717D42}"/>
+    <hyperlink ref="E53" r:id="rId26" xr:uid="{047ED4CC-5C21-4626-88F6-5FC8BF717D42}"/>
     <hyperlink ref="D2" r:id="rId27" xr:uid="{5EA29408-AF76-4487-95D5-EBA6B359D47F}"/>
     <hyperlink ref="D3" r:id="rId28" xr:uid="{96CB2BCC-A5EC-485B-9D31-0A951023FBEE}"/>
     <hyperlink ref="D4" r:id="rId29" xr:uid="{8EEA5B90-7272-496A-8B8E-05147344EE67}"/>
-    <hyperlink ref="E30" r:id="rId30" xr:uid="{EDF89984-41DC-428C-8A06-A5219D2F2064}"/>
-    <hyperlink ref="E31" r:id="rId31" xr:uid="{963EF514-45F6-41B5-8A0B-170A2C5ED925}"/>
-    <hyperlink ref="E32" r:id="rId32" xr:uid="{0541AB64-B50E-4219-BAEB-29954AE6C189}"/>
-    <hyperlink ref="E35" r:id="rId33" xr:uid="{601039D8-147B-4A85-B635-6E59BA7A2244}"/>
-    <hyperlink ref="E39" r:id="rId34" xr:uid="{7564D6D7-CED9-4D38-BBD7-C2EEA78F1308}"/>
-    <hyperlink ref="E37" r:id="rId35" xr:uid="{F1B28719-9C73-4CA8-91D4-84394F1BF02D}"/>
-    <hyperlink ref="E36" r:id="rId36" xr:uid="{46B0625B-ED5E-40A2-8233-AF6C3C10EBD9}"/>
-    <hyperlink ref="E40" r:id="rId37" xr:uid="{6624FAE6-B969-40BE-A83C-00E8C8E8107F}"/>
-    <hyperlink ref="E41" r:id="rId38" xr:uid="{FCDD24C9-7BEC-4ED4-879C-62F1D5248DE6}"/>
-    <hyperlink ref="E34" r:id="rId39" xr:uid="{E368D647-630A-427B-B878-286A42748400}"/>
-    <hyperlink ref="E33" r:id="rId40" xr:uid="{E2835FD3-57C4-45F7-AADC-A649C55446B5}"/>
-    <hyperlink ref="E42" r:id="rId41" xr:uid="{08C6F825-C2F3-4C5A-9844-FCA3A713F68D}"/>
-    <hyperlink ref="E38" r:id="rId42" xr:uid="{D152971E-7BC5-4FDF-AC3C-70B542BD6FCF}"/>
-    <hyperlink ref="E43" r:id="rId43" xr:uid="{EE360B1E-4D3C-4B17-BE11-666C855307BC}"/>
-    <hyperlink ref="E27" r:id="rId44" xr:uid="{E88A01CD-9D0A-4CB0-B261-AD9782F0FDB5}"/>
-    <hyperlink ref="E28" r:id="rId45" xr:uid="{79E85FCD-9DE4-4D29-8E73-74087A5E1F26}"/>
-    <hyperlink ref="E14" r:id="rId46" xr:uid="{C6202BE2-BE15-4B76-8999-8AAA70770870}"/>
+    <hyperlink ref="E31" r:id="rId30" xr:uid="{EDF89984-41DC-428C-8A06-A5219D2F2064}"/>
+    <hyperlink ref="E32" r:id="rId31" xr:uid="{963EF514-45F6-41B5-8A0B-170A2C5ED925}"/>
+    <hyperlink ref="E33" r:id="rId32" xr:uid="{0541AB64-B50E-4219-BAEB-29954AE6C189}"/>
+    <hyperlink ref="E40" r:id="rId33" xr:uid="{601039D8-147B-4A85-B635-6E59BA7A2244}"/>
+    <hyperlink ref="E45" r:id="rId34" xr:uid="{7564D6D7-CED9-4D38-BBD7-C2EEA78F1308}"/>
+    <hyperlink ref="E42" r:id="rId35" xr:uid="{F1B28719-9C73-4CA8-91D4-84394F1BF02D}"/>
+    <hyperlink ref="E46" r:id="rId36" xr:uid="{6624FAE6-B969-40BE-A83C-00E8C8E8107F}"/>
+    <hyperlink ref="E47" r:id="rId37" xr:uid="{FCDD24C9-7BEC-4ED4-879C-62F1D5248DE6}"/>
+    <hyperlink ref="E39" r:id="rId38" xr:uid="{E368D647-630A-427B-B878-286A42748400}"/>
+    <hyperlink ref="E34" r:id="rId39" xr:uid="{E2835FD3-57C4-45F7-AADC-A649C55446B5}"/>
+    <hyperlink ref="E48" r:id="rId40" xr:uid="{08C6F825-C2F3-4C5A-9844-FCA3A713F68D}"/>
+    <hyperlink ref="E44" r:id="rId41" xr:uid="{D152971E-7BC5-4FDF-AC3C-70B542BD6FCF}"/>
+    <hyperlink ref="E49" r:id="rId42" xr:uid="{EE360B1E-4D3C-4B17-BE11-666C855307BC}"/>
+    <hyperlink ref="E28" r:id="rId43" xr:uid="{E88A01CD-9D0A-4CB0-B261-AD9782F0FDB5}"/>
+    <hyperlink ref="E29" r:id="rId44" xr:uid="{79E85FCD-9DE4-4D29-8E73-74087A5E1F26}"/>
+    <hyperlink ref="E14" r:id="rId45" xr:uid="{C6202BE2-BE15-4B76-8999-8AAA70770870}"/>
+    <hyperlink ref="E41" r:id="rId46" xr:uid="{2A5B6187-0830-40C0-A2CC-35691E2933EE}"/>
+    <hyperlink ref="E43" r:id="rId47" xr:uid="{A34177A3-D1AC-413C-A195-EB5CA75C8BB5}"/>
+    <hyperlink ref="E54" r:id="rId48" xr:uid="{9AE0ADC8-D3C7-4A2A-A622-8A0575249604}"/>
+    <hyperlink ref="E35" r:id="rId49" xr:uid="{8360B823-DC3B-48E6-BF86-0C0AB26F13B9}"/>
+    <hyperlink ref="E37" r:id="rId50" xr:uid="{8F47EBFF-3FB3-4A86-AC11-A1065C310E90}"/>
+    <hyperlink ref="E38" r:id="rId51" xr:uid="{AADB1F37-73D0-48DE-AF52-F0DA1772A9F6}"/>
+    <hyperlink ref="E24" r:id="rId52" xr:uid="{71DB3019-4FE0-4285-A912-DD6C89147BAE}"/>
+    <hyperlink ref="E36" r:id="rId53" xr:uid="{DF484DA9-0C6C-4F08-8E2A-6BCB990D05B3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="262" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId47"/>
+  <pageSetup paperSize="262" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId54"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35051E3-80A1-4EBE-808C-93CF2367A231}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="3" width="62.6328125" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" customWidth="1"/>
+    <col min="5" max="5" width="22.90625" customWidth="1"/>
+    <col min="6" max="6" width="39" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
@@ -1882,10 +2090,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -1893,66 +2101,480 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>85</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
+      <c r="A3" s="6">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="5">
+        <v>625515</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{960FCF17-0FEC-4331-AFB1-F10FDFCF86FA}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{BDD3E217-9437-4B21-9A28-68965C92C2A9}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{FD5BC05D-18EA-4519-9D03-7C5500113CCF}"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://www.homedepot.com/p/Frost-King-5-16-in-x-1-4-in-x-17-ft-Black-EPDM-Cellular-Rubber-Weatherstrip-Tape-V25BK/202844545" xr:uid="{C3F1D196-C7E4-4977-AB01-F318BBC167E9}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{51547DFE-850C-4408-B034-FC3F9F186C23}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{9AD0134C-702D-4771-9418-693FB2E10B2D}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{AB3F6020-A10D-4749-8C64-95643ADD90B6}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{8E9F9936-0A0E-4B38-9A6F-46C1CFD2798B}"/>
+    <hyperlink ref="E9" r:id="rId7" xr:uid="{8E299AD7-8AA5-48B2-B902-61C374AA9D62}"/>
+    <hyperlink ref="E12" r:id="rId8" xr:uid="{1AAE300A-BD88-4173-879A-5C1435D7B6B1}"/>
+    <hyperlink ref="E17" r:id="rId9" xr:uid="{EF550965-DF9A-49AB-AC21-DE3E311EFFE0}"/>
+    <hyperlink ref="E14" r:id="rId10" xr:uid="{907BC2CA-964A-41C6-88C7-9F8D636A9BD5}"/>
+    <hyperlink ref="E18" r:id="rId11" xr:uid="{E292C02D-4A23-4D97-84A1-FD530A29CC6E}"/>
+    <hyperlink ref="E11" r:id="rId12" xr:uid="{2BC99DCE-D1AF-44D2-94F8-B472AD4B9EEF}"/>
+    <hyperlink ref="E10" r:id="rId13" xr:uid="{FD9437D8-87EE-4699-B74F-AB834FDFEB05}"/>
+    <hyperlink ref="E16" r:id="rId14" xr:uid="{60EDA2D9-B04B-46B4-A4C5-4381C90B6AD1}"/>
+    <hyperlink ref="E13" r:id="rId15" xr:uid="{6C5DCA4D-D1C1-4AF0-8F16-04832F28F7F5}"/>
+    <hyperlink ref="E15" r:id="rId16" xr:uid="{45FB8F6E-5980-46DC-90E7-2DE97D05344C}"/>
+    <hyperlink ref="E19" r:id="rId17" xr:uid="{46841DCD-CB8F-48D3-BF5E-1533C3F9E398}"/>
+    <hyperlink ref="E20" r:id="rId18" xr:uid="{8601945C-78FC-4303-889D-B74CCBA109FD}"/>
+    <hyperlink ref="E21" r:id="rId19" xr:uid="{90999296-D255-42F0-8B2F-5338AFD87497}"/>
+    <hyperlink ref="E23" r:id="rId20" xr:uid="{C4FE82D9-A73F-4B13-ABF1-E4478854B57B}"/>
+    <hyperlink ref="E24" r:id="rId21" xr:uid="{0FAD8755-829D-4070-8901-155EB321FE52}"/>
+    <hyperlink ref="E22" r:id="rId22" xr:uid="{CB01AF6C-07C6-4710-9EF8-B0A4F516AC8F}"/>
+    <hyperlink ref="E8" r:id="rId23" xr:uid="{8E0603A7-2B46-4AF6-AAC8-800F374AA40E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
